--- a/data/industry/CFM/LPDDR.xlsx
+++ b/data/industry/CFM/LPDDR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7790A06-47DA-48A0-92D2-134B9B917A54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFB8BEB0-BEC4-48AD-BAB1-8BB9F553B300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LPDDR4X 96GB" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,11 @@
     <sheet name="LPDDR4X 48GB" sheetId="3" r:id="rId3"/>
     <sheet name="LPDDR4X 32GB" sheetId="4" r:id="rId4"/>
     <sheet name="LPDDR4X 16GB" sheetId="5" r:id="rId5"/>
+    <sheet name="LPDDR5X 128GB" sheetId="6" r:id="rId6"/>
+    <sheet name="LPDDR5X 96GB" sheetId="7" r:id="rId7"/>
+    <sheet name="LPDDR5X 64GB" sheetId="8" r:id="rId8"/>
+    <sheet name="LPDDR5X 48GB" sheetId="9" r:id="rId9"/>
+    <sheet name="LPDDR5X 32GB" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -71,23 +76,23 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="179" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -100,7 +105,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -110,6 +115,14 @@
       <color theme="1"/>
       <name val="Verdana"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -131,41 +144,64 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
@@ -447,19 +483,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G44"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="11.19921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -482,7 +518,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>45860</v>
       </c>
@@ -505,7 +541,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>45867</v>
       </c>
@@ -528,7 +564,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>45874</v>
       </c>
@@ -551,7 +587,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>45881</v>
       </c>
@@ -574,7 +610,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>45888</v>
       </c>
@@ -597,7 +633,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="1">
         <v>45895</v>
       </c>
@@ -620,7 +656,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="1">
         <v>45902</v>
       </c>
@@ -643,7 +679,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="1">
         <v>45909</v>
       </c>
@@ -666,7 +702,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="1">
         <v>45916</v>
       </c>
@@ -689,7 +725,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="1">
         <v>45923</v>
       </c>
@@ -712,7 +748,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="1">
         <v>45930</v>
       </c>
@@ -735,7 +771,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="1">
         <v>45944</v>
       </c>
@@ -758,7 +794,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="1">
         <v>45951</v>
       </c>
@@ -781,7 +817,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="1">
         <v>45958</v>
       </c>
@@ -804,7 +840,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="1">
         <v>45965</v>
       </c>
@@ -827,7 +863,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="1">
         <v>45972</v>
       </c>
@@ -850,7 +886,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="1">
         <v>45979</v>
       </c>
@@ -873,7 +909,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="1">
         <v>45986</v>
       </c>
@@ -896,7 +932,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="1">
         <v>45993</v>
       </c>
@@ -919,7 +955,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="1">
         <v>46000</v>
       </c>
@@ -942,7 +978,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="1">
         <v>46007</v>
       </c>
@@ -965,7 +1001,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="1">
         <v>46014</v>
       </c>
@@ -988,7 +1024,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="1">
         <v>46021</v>
       </c>
@@ -1011,7 +1047,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="1">
         <v>46028</v>
       </c>
@@ -1034,7 +1070,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="4">
         <v>46035</v>
       </c>
@@ -1057,7 +1093,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="4">
         <v>46042</v>
       </c>
@@ -1080,7 +1116,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="1">
         <v>46049</v>
       </c>
@@ -1103,7 +1139,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="4">
         <v>46056</v>
       </c>
@@ -1126,7 +1162,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="4">
         <v>46063</v>
       </c>
@@ -1149,7 +1185,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="4">
         <v>46077</v>
       </c>
@@ -1172,7 +1208,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="4">
         <v>46084</v>
       </c>
@@ -1195,7 +1231,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="4">
         <v>46091</v>
       </c>
@@ -1218,7 +1254,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="4">
         <v>46098</v>
       </c>
@@ -1241,7 +1277,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="4">
         <v>46105</v>
       </c>
@@ -1264,7 +1300,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="4">
         <v>46112</v>
       </c>
@@ -1287,7 +1323,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="4">
         <v>46119</v>
       </c>
@@ -1310,7 +1346,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="4">
         <v>46126</v>
       </c>
@@ -1333,7 +1369,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="4">
         <v>46133</v>
       </c>
@@ -1355,6 +1391,64 @@
       <c r="G39" s="11">
         <v>140</v>
       </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="4">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="4">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="11">
+        <v>138.5</v>
+      </c>
+      <c r="F40" s="11">
+        <v>142.5</v>
+      </c>
+      <c r="G40" s="11">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="4">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="4">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="11">
+        <v>138.5</v>
+      </c>
+      <c r="F41" s="11">
+        <v>142.5</v>
+      </c>
+      <c r="G41" s="11">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="8"/>
+      <c r="B43" s="8"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="8"/>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="8"/>
+      <c r="B44" s="8"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -1363,21 +1457,155 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6A21211-5672-4A48-88B4-9571364FB5C8}">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="12.6640625" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="17" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9" style="20"/>
+    <col min="7" max="7" width="11.21875" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="18">
+        <v>46161</v>
+      </c>
+      <c r="B2" s="18">
+        <v>46161</v>
+      </c>
+      <c r="C2" s="16">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="20">
+        <v>50</v>
+      </c>
+      <c r="F2" s="20">
+        <v>60</v>
+      </c>
+      <c r="G2" s="20">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="18">
+        <v>46168</v>
+      </c>
+      <c r="B3" s="18">
+        <v>46168</v>
+      </c>
+      <c r="C3" s="16">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="20">
+        <v>49</v>
+      </c>
+      <c r="F3" s="20">
+        <v>59</v>
+      </c>
+      <c r="G3" s="20">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="18">
+        <v>46175</v>
+      </c>
+      <c r="B4" s="18">
+        <v>46175</v>
+      </c>
+      <c r="C4" s="16">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="20">
+        <v>49</v>
+      </c>
+      <c r="F4" s="20">
+        <v>59</v>
+      </c>
+      <c r="G4" s="20">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="18">
+        <v>46182</v>
+      </c>
+      <c r="B5" s="18">
+        <v>46182</v>
+      </c>
+      <c r="C5" s="16">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="20">
+        <v>49</v>
+      </c>
+      <c r="F5" s="20">
+        <v>59</v>
+      </c>
+      <c r="G5" s="20">
+        <v>54</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C002ACE-9D35-4283-B798-CF0C9347B851}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="11.19921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1400,7 +1628,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>45860</v>
       </c>
@@ -1423,7 +1651,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>45867</v>
       </c>
@@ -1446,7 +1674,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>45874</v>
       </c>
@@ -1469,7 +1697,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>45881</v>
       </c>
@@ -1492,7 +1720,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>45888</v>
       </c>
@@ -1515,7 +1743,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="1">
         <v>45895</v>
       </c>
@@ -1538,7 +1766,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="1">
         <v>45902</v>
       </c>
@@ -1561,7 +1789,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="1">
         <v>45909</v>
       </c>
@@ -1584,7 +1812,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="1">
         <v>45916</v>
       </c>
@@ -1607,7 +1835,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="1">
         <v>45923</v>
       </c>
@@ -1630,7 +1858,7 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="1">
         <v>45930</v>
       </c>
@@ -1653,7 +1881,7 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="1">
         <v>45944</v>
       </c>
@@ -1676,7 +1904,7 @@
         <v>28.5</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="1">
         <v>45951</v>
       </c>
@@ -1699,7 +1927,7 @@
         <v>28.5</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="1">
         <v>45958</v>
       </c>
@@ -1722,7 +1950,7 @@
         <v>28.5</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="1">
         <v>45965</v>
       </c>
@@ -1745,7 +1973,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="1">
         <v>45972</v>
       </c>
@@ -1768,7 +1996,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="1">
         <v>45979</v>
       </c>
@@ -1791,7 +2019,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="1">
         <v>45986</v>
       </c>
@@ -1814,7 +2042,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="1">
         <v>45993</v>
       </c>
@@ -1837,7 +2065,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="1">
         <v>46000</v>
       </c>
@@ -1860,7 +2088,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="1">
         <v>46007</v>
       </c>
@@ -1883,7 +2111,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="1">
         <v>46014</v>
       </c>
@@ -1906,7 +2134,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="1">
         <v>46021</v>
       </c>
@@ -1929,7 +2157,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="1">
         <v>46028</v>
       </c>
@@ -1952,7 +2180,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="4">
         <v>46035</v>
       </c>
@@ -1975,7 +2203,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="4">
         <v>46042</v>
       </c>
@@ -1998,7 +2226,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="1">
         <v>46049</v>
       </c>
@@ -2021,7 +2249,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="4">
         <v>46056</v>
       </c>
@@ -2044,7 +2272,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="4">
         <v>46063</v>
       </c>
@@ -2067,7 +2295,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="4">
         <v>46077</v>
       </c>
@@ -2090,7 +2318,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="4">
         <v>46084</v>
       </c>
@@ -2113,7 +2341,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="4">
         <v>46091</v>
       </c>
@@ -2136,7 +2364,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="4">
         <v>46098</v>
       </c>
@@ -2159,7 +2387,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="4">
         <v>46105</v>
       </c>
@@ -2182,7 +2410,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="4">
         <v>46112</v>
       </c>
@@ -2205,7 +2433,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="4">
         <v>46119</v>
       </c>
@@ -2228,7 +2456,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="4">
         <v>46126</v>
       </c>
@@ -2251,7 +2479,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="4">
         <v>46133</v>
       </c>
@@ -2272,6 +2500,144 @@
       </c>
       <c r="G39" s="11">
         <v>103</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="4">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="4">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="11">
+        <v>101.2</v>
+      </c>
+      <c r="F40" s="11">
+        <v>105</v>
+      </c>
+      <c r="G40" s="11">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="4">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="4">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="11">
+        <v>98</v>
+      </c>
+      <c r="F41" s="11">
+        <v>102</v>
+      </c>
+      <c r="G41" s="11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="4">
+        <v>46161</v>
+      </c>
+      <c r="B42" s="4">
+        <v>46161</v>
+      </c>
+      <c r="C42" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="11">
+        <v>98</v>
+      </c>
+      <c r="F42" s="11">
+        <v>102</v>
+      </c>
+      <c r="G42" s="11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="4">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="4">
+        <v>46168</v>
+      </c>
+      <c r="C43" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="11">
+        <v>98</v>
+      </c>
+      <c r="F43" s="11">
+        <v>102</v>
+      </c>
+      <c r="G43" s="11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="4">
+        <v>46175</v>
+      </c>
+      <c r="B44" s="4">
+        <v>46175</v>
+      </c>
+      <c r="C44" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="11">
+        <v>98</v>
+      </c>
+      <c r="F44" s="11">
+        <v>102</v>
+      </c>
+      <c r="G44" s="11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="4">
+        <v>46182</v>
+      </c>
+      <c r="B45" s="4">
+        <v>46182</v>
+      </c>
+      <c r="C45" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="11">
+        <v>98</v>
+      </c>
+      <c r="F45" s="11">
+        <v>102</v>
+      </c>
+      <c r="G45" s="11">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -2282,19 +2648,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B598A90B-5FE2-4525-ACAE-8E4129C35604}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="11.19921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -2317,7 +2683,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>45860</v>
       </c>
@@ -2340,7 +2706,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>45867</v>
       </c>
@@ -2363,7 +2729,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>45874</v>
       </c>
@@ -2386,7 +2752,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>45881</v>
       </c>
@@ -2409,7 +2775,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>45888</v>
       </c>
@@ -2432,7 +2798,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="1">
         <v>45895</v>
       </c>
@@ -2455,7 +2821,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="1">
         <v>45902</v>
       </c>
@@ -2478,7 +2844,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="1">
         <v>45909</v>
       </c>
@@ -2501,7 +2867,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="1">
         <v>45916</v>
       </c>
@@ -2524,7 +2890,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="1">
         <v>45923</v>
       </c>
@@ -2547,7 +2913,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="1">
         <v>45930</v>
       </c>
@@ -2570,7 +2936,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="1">
         <v>45944</v>
       </c>
@@ -2593,7 +2959,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="1">
         <v>45951</v>
       </c>
@@ -2616,7 +2982,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="1">
         <v>45958</v>
       </c>
@@ -2639,7 +3005,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="1">
         <v>45965</v>
       </c>
@@ -2662,7 +3028,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="1">
         <v>45972</v>
       </c>
@@ -2685,7 +3051,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="1">
         <v>45979</v>
       </c>
@@ -2708,7 +3074,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="1">
         <v>45986</v>
       </c>
@@ -2731,7 +3097,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="1">
         <v>45993</v>
       </c>
@@ -2754,7 +3120,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="1">
         <v>46000</v>
       </c>
@@ -2777,7 +3143,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="1">
         <v>46007</v>
       </c>
@@ -2800,7 +3166,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="1">
         <v>46014</v>
       </c>
@@ -2823,7 +3189,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="1">
         <v>46021</v>
       </c>
@@ -2846,7 +3212,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="1">
         <v>46028</v>
       </c>
@@ -2869,7 +3235,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="4">
         <v>46035</v>
       </c>
@@ -2892,7 +3258,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="4">
         <v>46042</v>
       </c>
@@ -2915,7 +3281,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="1">
         <v>46049</v>
       </c>
@@ -2938,7 +3304,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="4">
         <v>46056</v>
       </c>
@@ -2961,7 +3327,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="4">
         <v>46063</v>
       </c>
@@ -2984,7 +3350,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="4">
         <v>46077</v>
       </c>
@@ -3007,7 +3373,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="4">
         <v>46084</v>
       </c>
@@ -3030,7 +3396,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="4">
         <v>46091</v>
       </c>
@@ -3053,7 +3419,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="4">
         <v>46098</v>
       </c>
@@ -3076,7 +3442,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="4">
         <v>46105</v>
       </c>
@@ -3099,7 +3465,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="4">
         <v>46112</v>
       </c>
@@ -3122,7 +3488,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="4">
         <v>46119</v>
       </c>
@@ -3145,7 +3511,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="4">
         <v>46126</v>
       </c>
@@ -3168,7 +3534,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="4">
         <v>46133</v>
       </c>
@@ -3189,6 +3555,144 @@
       </c>
       <c r="G39" s="11">
         <v>80</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="4">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="4">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="11">
+        <v>78.5</v>
+      </c>
+      <c r="F40" s="11">
+        <v>82</v>
+      </c>
+      <c r="G40" s="11">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="4">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="4">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="11">
+        <v>72</v>
+      </c>
+      <c r="F41" s="11">
+        <v>79</v>
+      </c>
+      <c r="G41" s="11">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="4">
+        <v>46161</v>
+      </c>
+      <c r="B42" s="4">
+        <v>46161</v>
+      </c>
+      <c r="C42" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="11">
+        <v>72</v>
+      </c>
+      <c r="F42" s="11">
+        <v>79</v>
+      </c>
+      <c r="G42" s="11">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="4">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="4">
+        <v>46168</v>
+      </c>
+      <c r="C43" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="11">
+        <v>70</v>
+      </c>
+      <c r="F43" s="11">
+        <v>77</v>
+      </c>
+      <c r="G43" s="11">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="4">
+        <v>46175</v>
+      </c>
+      <c r="B44" s="4">
+        <v>46175</v>
+      </c>
+      <c r="C44" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="11">
+        <v>70</v>
+      </c>
+      <c r="F44" s="11">
+        <v>77</v>
+      </c>
+      <c r="G44" s="11">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="4">
+        <v>46182</v>
+      </c>
+      <c r="B45" s="4">
+        <v>46182</v>
+      </c>
+      <c r="C45" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="11">
+        <v>70</v>
+      </c>
+      <c r="F45" s="11">
+        <v>77</v>
+      </c>
+      <c r="G45" s="11">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -3199,18 +3703,18 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D1E626F-37CF-4B96-A920-7652799AAE80}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="9" style="11"/>
     <col min="8" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -3233,7 +3737,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>45860</v>
       </c>
@@ -3256,7 +3760,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>45867</v>
       </c>
@@ -3279,7 +3783,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>45874</v>
       </c>
@@ -3302,7 +3806,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>45881</v>
       </c>
@@ -3325,7 +3829,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>45888</v>
       </c>
@@ -3348,7 +3852,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="1">
         <v>45895</v>
       </c>
@@ -3371,7 +3875,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="1">
         <v>45902</v>
       </c>
@@ -3394,7 +3898,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="1">
         <v>45909</v>
       </c>
@@ -3417,7 +3921,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="1">
         <v>45916</v>
       </c>
@@ -3440,7 +3944,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="1">
         <v>45923</v>
       </c>
@@ -3463,7 +3967,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="1">
         <v>45930</v>
       </c>
@@ -3486,7 +3990,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="1">
         <v>45944</v>
       </c>
@@ -3509,7 +4013,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="1">
         <v>45951</v>
       </c>
@@ -3532,7 +4036,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="1">
         <v>45958</v>
       </c>
@@ -3555,7 +4059,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="1">
         <v>45965</v>
       </c>
@@ -3578,7 +4082,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="1">
         <v>45972</v>
       </c>
@@ -3601,7 +4105,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="1">
         <v>45979</v>
       </c>
@@ -3624,7 +4128,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="1">
         <v>45986</v>
       </c>
@@ -3647,7 +4151,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="1">
         <v>45993</v>
       </c>
@@ -3670,7 +4174,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="1">
         <v>46000</v>
       </c>
@@ -3693,7 +4197,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="1">
         <v>46007</v>
       </c>
@@ -3716,7 +4220,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="1">
         <v>46014</v>
       </c>
@@ -3739,7 +4243,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="1">
         <v>46021</v>
       </c>
@@ -3762,7 +4266,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="1">
         <v>46028</v>
       </c>
@@ -3785,7 +4289,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="4">
         <v>46035</v>
       </c>
@@ -3808,7 +4312,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="4">
         <v>46042</v>
       </c>
@@ -3831,7 +4335,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="1">
         <v>46049</v>
       </c>
@@ -3854,7 +4358,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="4">
         <v>46056</v>
       </c>
@@ -3877,7 +4381,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="4">
         <v>46063</v>
       </c>
@@ -3900,7 +4404,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="4">
         <v>46077</v>
       </c>
@@ -3923,7 +4427,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="4">
         <v>46084</v>
       </c>
@@ -3946,7 +4450,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="4">
         <v>46091</v>
       </c>
@@ -3969,7 +4473,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="4">
         <v>46098</v>
       </c>
@@ -3992,7 +4496,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="4">
         <v>46105</v>
       </c>
@@ -4015,7 +4519,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="4">
         <v>46112</v>
       </c>
@@ -4038,7 +4542,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="4">
         <v>46119</v>
       </c>
@@ -4061,7 +4565,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="4">
         <v>46126</v>
       </c>
@@ -4084,7 +4588,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="4">
         <v>46133</v>
       </c>
@@ -4105,6 +4609,144 @@
       </c>
       <c r="G39" s="11">
         <v>60</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="4">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="4">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="11">
+        <v>59</v>
+      </c>
+      <c r="F40" s="11">
+        <v>61.5</v>
+      </c>
+      <c r="G40" s="11">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="4">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="4">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="11">
+        <v>50</v>
+      </c>
+      <c r="F41" s="11">
+        <v>60</v>
+      </c>
+      <c r="G41" s="11">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="4">
+        <v>46161</v>
+      </c>
+      <c r="B42" s="4">
+        <v>46161</v>
+      </c>
+      <c r="C42" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="11">
+        <v>50</v>
+      </c>
+      <c r="F42" s="11">
+        <v>60</v>
+      </c>
+      <c r="G42" s="11">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="4">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="4">
+        <v>46168</v>
+      </c>
+      <c r="C43" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="11">
+        <v>49</v>
+      </c>
+      <c r="F43" s="11">
+        <v>59</v>
+      </c>
+      <c r="G43" s="11">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="4">
+        <v>46175</v>
+      </c>
+      <c r="B44" s="4">
+        <v>46175</v>
+      </c>
+      <c r="C44" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="11">
+        <v>49</v>
+      </c>
+      <c r="F44" s="11">
+        <v>59</v>
+      </c>
+      <c r="G44" s="11">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="4">
+        <v>46182</v>
+      </c>
+      <c r="B45" s="4">
+        <v>46182</v>
+      </c>
+      <c r="C45" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="11">
+        <v>49</v>
+      </c>
+      <c r="F45" s="11">
+        <v>59</v>
+      </c>
+      <c r="G45" s="11">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -4115,19 +4757,19 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EF2AA72-B42E-4BE9-BF50-F231D4EF8093}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="11.19921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -4150,7 +4792,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>45860</v>
       </c>
@@ -4173,7 +4815,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>45867</v>
       </c>
@@ -4196,7 +4838,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>45874</v>
       </c>
@@ -4219,7 +4861,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>45881</v>
       </c>
@@ -4242,7 +4884,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>45888</v>
       </c>
@@ -4265,7 +4907,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="1">
         <v>45895</v>
       </c>
@@ -4288,7 +4930,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="1">
         <v>45902</v>
       </c>
@@ -4311,7 +4953,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="1">
         <v>45909</v>
       </c>
@@ -4334,7 +4976,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="1">
         <v>45916</v>
       </c>
@@ -4357,7 +4999,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="1">
         <v>45923</v>
       </c>
@@ -4380,7 +5022,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="1">
         <v>45930</v>
       </c>
@@ -4403,7 +5045,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="1">
         <v>45944</v>
       </c>
@@ -4426,7 +5068,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="1">
         <v>45951</v>
       </c>
@@ -4449,7 +5091,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="1">
         <v>45958</v>
       </c>
@@ -4472,7 +5114,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="1">
         <v>45965</v>
       </c>
@@ -4495,7 +5137,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="1">
         <v>45972</v>
       </c>
@@ -4518,7 +5160,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="1">
         <v>45979</v>
       </c>
@@ -4541,7 +5183,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="1">
         <v>45986</v>
       </c>
@@ -4564,7 +5206,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="1">
         <v>45993</v>
       </c>
@@ -4587,7 +5229,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="1">
         <v>46000</v>
       </c>
@@ -4610,7 +5252,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="1">
         <v>46007</v>
       </c>
@@ -4633,7 +5275,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="1">
         <v>46014</v>
       </c>
@@ -4656,7 +5298,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="1">
         <v>46021</v>
       </c>
@@ -4679,7 +5321,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="1">
         <v>46028</v>
       </c>
@@ -4702,7 +5344,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="4">
         <v>46035</v>
       </c>
@@ -4725,7 +5367,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="4">
         <v>46042</v>
       </c>
@@ -4748,7 +5390,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="1">
         <v>46049</v>
       </c>
@@ -4771,7 +5413,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="4">
         <v>46056</v>
       </c>
@@ -4794,7 +5436,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="4">
         <v>46063</v>
       </c>
@@ -4817,7 +5459,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="4">
         <v>46077</v>
       </c>
@@ -4840,7 +5482,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="4">
         <v>46084</v>
       </c>
@@ -4863,7 +5505,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="4">
         <v>46091</v>
       </c>
@@ -4886,7 +5528,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="4">
         <v>46098</v>
       </c>
@@ -4909,7 +5551,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="4">
         <v>46105</v>
       </c>
@@ -4932,7 +5574,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="4">
         <v>46112</v>
       </c>
@@ -4955,7 +5597,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="4">
         <v>46119</v>
       </c>
@@ -4978,7 +5620,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="4">
         <v>46126</v>
       </c>
@@ -5001,7 +5643,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="4">
         <v>46133</v>
       </c>
@@ -5021,6 +5663,144 @@
         <v>31.8</v>
       </c>
       <c r="G39" s="11">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="4">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="4">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="11">
+        <v>30.5</v>
+      </c>
+      <c r="F40" s="11">
+        <v>31.8</v>
+      </c>
+      <c r="G40" s="11">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="4">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="4">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="11">
+        <v>30.5</v>
+      </c>
+      <c r="F41" s="11">
+        <v>31.8</v>
+      </c>
+      <c r="G41" s="11">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="4">
+        <v>46161</v>
+      </c>
+      <c r="B42" s="4">
+        <v>46161</v>
+      </c>
+      <c r="C42" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="11">
+        <v>30.5</v>
+      </c>
+      <c r="F42" s="11">
+        <v>31.8</v>
+      </c>
+      <c r="G42" s="11">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="4">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="4">
+        <v>46168</v>
+      </c>
+      <c r="C43" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="11">
+        <v>30.5</v>
+      </c>
+      <c r="F43" s="11">
+        <v>31.8</v>
+      </c>
+      <c r="G43" s="11">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="4">
+        <v>46175</v>
+      </c>
+      <c r="B44" s="4">
+        <v>46175</v>
+      </c>
+      <c r="C44" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="11">
+        <v>30.5</v>
+      </c>
+      <c r="F44" s="11">
+        <v>31.8</v>
+      </c>
+      <c r="G44" s="11">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="4">
+        <v>46182</v>
+      </c>
+      <c r="B45" s="4">
+        <v>46182</v>
+      </c>
+      <c r="C45" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="11">
+        <v>30.5</v>
+      </c>
+      <c r="F45" s="11">
+        <v>31.8</v>
+      </c>
+      <c r="G45" s="11">
         <v>31</v>
       </c>
     </row>
@@ -5028,4 +5808,540 @@
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02799ACD-F3A2-408F-864F-69E943B68184}">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="12.6640625" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="17" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9" style="20"/>
+    <col min="7" max="7" width="11.21875" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="18">
+        <v>46161</v>
+      </c>
+      <c r="B2" s="18">
+        <v>46161</v>
+      </c>
+      <c r="C2" s="16">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="20">
+        <v>216</v>
+      </c>
+      <c r="F2" s="20">
+        <v>226</v>
+      </c>
+      <c r="G2" s="20">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="18">
+        <v>46168</v>
+      </c>
+      <c r="B3" s="18">
+        <v>46168</v>
+      </c>
+      <c r="C3" s="16">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="20">
+        <v>216</v>
+      </c>
+      <c r="F3" s="20">
+        <v>226</v>
+      </c>
+      <c r="G3" s="20">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="18">
+        <v>46175</v>
+      </c>
+      <c r="B4" s="18">
+        <v>46175</v>
+      </c>
+      <c r="C4" s="16">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="20">
+        <v>216</v>
+      </c>
+      <c r="F4" s="20">
+        <v>226</v>
+      </c>
+      <c r="G4" s="20">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="18">
+        <v>46182</v>
+      </c>
+      <c r="B5" s="18">
+        <v>46182</v>
+      </c>
+      <c r="C5" s="16">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="20">
+        <v>216</v>
+      </c>
+      <c r="F5" s="20">
+        <v>226</v>
+      </c>
+      <c r="G5" s="20">
+        <v>221</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36ED3A83-EAB3-4813-90B7-C7551CCA3B20}">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="12.6640625" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="17" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9" style="20"/>
+    <col min="7" max="7" width="11.21875" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="18">
+        <v>46161</v>
+      </c>
+      <c r="B2" s="18">
+        <v>46161</v>
+      </c>
+      <c r="C2" s="16">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="20">
+        <v>160</v>
+      </c>
+      <c r="F2" s="20">
+        <v>170</v>
+      </c>
+      <c r="G2" s="20">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="18">
+        <v>46168</v>
+      </c>
+      <c r="B3" s="18">
+        <v>46168</v>
+      </c>
+      <c r="C3" s="16">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="20">
+        <v>160</v>
+      </c>
+      <c r="F3" s="20">
+        <v>170</v>
+      </c>
+      <c r="G3" s="20">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="18">
+        <v>46175</v>
+      </c>
+      <c r="B4" s="18">
+        <v>46175</v>
+      </c>
+      <c r="C4" s="16">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="20">
+        <v>160</v>
+      </c>
+      <c r="F4" s="20">
+        <v>170</v>
+      </c>
+      <c r="G4" s="20">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="18">
+        <v>46182</v>
+      </c>
+      <c r="B5" s="18">
+        <v>46182</v>
+      </c>
+      <c r="C5" s="16">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="20">
+        <v>160</v>
+      </c>
+      <c r="F5" s="20">
+        <v>170</v>
+      </c>
+      <c r="G5" s="20">
+        <v>165</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A48A7DD7-D740-4DE5-96FE-EC5DB0F7F7D6}">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="12.6640625" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="17" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9" style="20"/>
+    <col min="7" max="7" width="11.21875" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="18">
+        <v>46161</v>
+      </c>
+      <c r="B2" s="18">
+        <v>46161</v>
+      </c>
+      <c r="C2" s="16">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="20">
+        <v>98</v>
+      </c>
+      <c r="F2" s="20">
+        <v>180</v>
+      </c>
+      <c r="G2" s="20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="18">
+        <v>46168</v>
+      </c>
+      <c r="B3" s="18">
+        <v>46168</v>
+      </c>
+      <c r="C3" s="16">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="20">
+        <v>98</v>
+      </c>
+      <c r="F3" s="20">
+        <v>180</v>
+      </c>
+      <c r="G3" s="20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="18">
+        <v>46175</v>
+      </c>
+      <c r="B4" s="18">
+        <v>46175</v>
+      </c>
+      <c r="C4" s="16">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="20">
+        <v>98</v>
+      </c>
+      <c r="F4" s="20">
+        <v>180</v>
+      </c>
+      <c r="G4" s="20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="18">
+        <v>46182</v>
+      </c>
+      <c r="B5" s="18">
+        <v>46182</v>
+      </c>
+      <c r="C5" s="16">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="20">
+        <v>98</v>
+      </c>
+      <c r="F5" s="20">
+        <v>180</v>
+      </c>
+      <c r="G5" s="20">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFDE94D2-A563-4C21-8A9D-D80E69343286}">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="12.6640625" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="17" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9" style="20"/>
+    <col min="7" max="7" width="11.21875" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="18">
+        <v>46161</v>
+      </c>
+      <c r="B2" s="18">
+        <v>46161</v>
+      </c>
+      <c r="C2" s="16">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="20">
+        <v>72</v>
+      </c>
+      <c r="F2" s="20">
+        <v>80</v>
+      </c>
+      <c r="G2" s="20">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="18">
+        <v>46168</v>
+      </c>
+      <c r="B3" s="18">
+        <v>46168</v>
+      </c>
+      <c r="C3" s="16">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="20">
+        <v>71</v>
+      </c>
+      <c r="F3" s="20">
+        <v>79</v>
+      </c>
+      <c r="G3" s="20">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="18">
+        <v>46175</v>
+      </c>
+      <c r="B4" s="18">
+        <v>46175</v>
+      </c>
+      <c r="C4" s="16">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="20">
+        <v>71</v>
+      </c>
+      <c r="F4" s="20">
+        <v>79</v>
+      </c>
+      <c r="G4" s="20">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="18">
+        <v>46182</v>
+      </c>
+      <c r="B5" s="18">
+        <v>46182</v>
+      </c>
+      <c r="C5" s="16">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="20">
+        <v>71</v>
+      </c>
+      <c r="F5" s="20">
+        <v>79</v>
+      </c>
+      <c r="G5" s="20">
+        <v>76</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>